--- a/yt/fixtures/master_list.xlsx
+++ b/yt/fixtures/master_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1497,51 +1497,51 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>arth_ep16_001</t>
+          <t>garf_film_001</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ARTH</t>
+          <t>GARF</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Arthur</t>
+          <t>Garfield and Friends</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Film</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>arth_ep16_002</t>
+          <t>garf_film_002</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ARTH</t>
+          <t>GARF</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Arthur</t>
+          <t>Garfield and Friends</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Film</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>arth_ep16_003</t>
+          <t>arth_ep16_001</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1563,7 +1563,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>arth_ep16_004</t>
+          <t>arth_ep16_002</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>arth_ep16_005</t>
+          <t>arth_ep16_003</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>arth_ep17_001</t>
+          <t>arth_ep16_004</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1622,14 +1622,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>arth_ep17_002</t>
+          <t>arth_ep16_005</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1644,14 +1644,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>arth_ep17_003</t>
+          <t>arth_ep17_001</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>arth_ep17_004</t>
+          <t>arth_ep17_002</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>arth_ep17_005</t>
+          <t>arth_ep17_003</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>arth_ep18_001</t>
+          <t>arth_ep17_004</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1732,14 +1732,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>arth_ep18_002</t>
+          <t>arth_ep17_005</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1754,14 +1754,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>arth_ep18_003</t>
+          <t>arth_ep18_001</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1783,7 +1783,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>arth_ep18_004</t>
+          <t>arth_ep18_002</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>arth_ep18_005</t>
+          <t>arth_ep18_003</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1827,7 +1827,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>arth_ep19_001</t>
+          <t>arth_ep18_004</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1842,14 +1842,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>arth_ep19_002</t>
+          <t>arth_ep18_005</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1864,14 +1864,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>arth_ep19_003</t>
+          <t>arth_ep19_001</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1893,7 +1893,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>arth_ep19_004</t>
+          <t>arth_ep19_002</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>arth_ep19_005</t>
+          <t>arth_ep19_003</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1937,43 +1937,51 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>anne_ep_001</t>
+          <t>arth_ep19_004</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ANNE01</t>
+          <t>ARTH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Anne with an E</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Arthur</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>anne_ep_002</t>
+          <t>arth_ep19_005</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ANNE01</t>
+          <t>ARTH</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Anne with an E</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Arthur</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>anne_ep_003</t>
+          <t>anne_ep_001</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1991,7 +1999,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>anne_ep_004</t>
+          <t>anne_ep_002</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2009,7 +2017,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>anne_ep_005</t>
+          <t>anne_ep_003</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2027,51 +2035,43 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>scmx_ep03_001</t>
+          <t>anne_ep_004</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SCMX</t>
+          <t>ANNE01</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Science Max</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>Anne with an E</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>scmx_ep03_002</t>
+          <t>anne_ep_005</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SCMX</t>
+          <t>ANNE01</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Science Max</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+          <t>Anne with an E</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>scmx_ep03_003</t>
+          <t>scmx_ep03_001</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2093,7 +2093,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>scmx_ep03_004</t>
+          <t>scmx_ep03_002</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2115,7 +2115,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>scmx_ep03_005</t>
+          <t>scmx_ep03_003</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2137,7 +2137,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>scmx_ep05_001</t>
+          <t>scmx_ep03_004</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2152,14 +2152,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>scmx_ep05_002</t>
+          <t>scmx_ep03_005</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2174,14 +2174,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>03</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>scmx_ep05_003</t>
+          <t>scmx_ep05_001</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2203,7 +2203,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>scmx_ep05_004</t>
+          <t>scmx_ep05_002</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2225,7 +2225,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>scmx_ep05_005</t>
+          <t>scmx_ep05_003</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2247,51 +2247,51 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>krma_ep_001</t>
+          <t>scmx_ep05_004</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KRMA</t>
+          <t>SCMX</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Karma's World</t>
+          <t>Science Max</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>krma_ep_002</t>
+          <t>scmx_ep05_005</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KRMA</t>
+          <t>SCMX</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Karma's World</t>
+          <t>Science Max</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>05</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>krma_ep_003</t>
+          <t>krma_ep_001</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>krma_ep_004</t>
+          <t>krma_ep_002</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2335,20 +2335,64 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>krma_ep_003</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>KRMA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Karma's World</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>krma_ep_004</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>KRMA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Karma's World</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>krma_ep_005</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>KRMA</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Karma's World</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>02</t>
         </is>
